--- a/checklist_forms/045_sports_trading_card_rookie_checklist--checklist_forms.xlsx
+++ b/checklist_forms/045_sports_trading_card_rookie_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>checklist_completed</t>
+          <t>checklist_completed_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Checklist Completed</t>
+          <t>Checklist Completed 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>checklist_reviewed</t>
+          <t>checklist_reviewed_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Checklist Reviewed</t>
+          <t>Checklist Reviewed 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>shop_name</t>
+          <t>shop_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shop Name</t>
+          <t>Shop Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>employee_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Employee Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_method_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contact Method</t>
+          <t>Contact Method 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1283,7 +1283,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
